--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260716085853</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -1157,7 +1157,7 @@
     <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260716085852</t>
   </si>
   <si>
     <t xml:space="preserve">con-1

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
